--- a/Assets/test260903/chapter0105.xlsx
+++ b/Assets/test260903/chapter0105.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="119" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB8A32F-0AA3-462D-8C8E-4938C6199CDF}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0105" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0105" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="56">
   <si>
     <t>Command</t>
   </si>
@@ -72,31 +81,216 @@
     <t>Chapter1-5です</t>
   </si>
   <si>
+    <t>*chapter0106_Start</t>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <t>Jump</t>
-  </si>
-  <si>
-    <t>*chapter0106_Start</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM2</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：ホテルのエントランス</t>
+  </si>
+  <si>
+    <t>最初に断っておくけれど、
+君は……何か勘違いしていますね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マネージャー</t>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>パワハラとか、過干渉とか、
+そういう話じゃありません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ちゃんと全部、彼女には話してあるし、
+彼女も了承してくれています</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希のマネージャーは落ち着いているが、
+ドスの効いた声で言った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……気圧されそうだ。
+向き合うだけで、逃げ出したくなる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>言葉も上手く出てこない。
+それでも、ここで退くのは絶対に嫌だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>その時、有希が口を開いた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+  </si>
+  <si>
+    <t>歌の仕事だって、
+まだ表に出ていないけど、写真集の企画も</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まず世間に知ってもらって、
+それから役者に仕事を移していく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全部、ちゃんと説明を受けて、
+それで私……やるって決めたの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>その通りです</t>
+    <rPh sb="2" eb="3">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>…………</t>
+  </si>
+  <si>
+    <t>…………</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……頑張ったよ。凄く頑張った。
+だって、あなたと……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>一番好きな人と、約束したんだもん。
+お互いの夢を叶えるって</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、できないの。
+どれだけ頑張っても、できないの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>歌の仕事だけは……全然できない
+プロの人たちに申し訳ないよ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>みんな気を遣ってくれてるけど、
+プロを名乗っていいレベルじゃないよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……ネガなこと言うのは、
+そこまでにしようよ。浪川さん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>君じゃプロの歌手には勝てません。
+だって君は、プロじゃないんですから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こういうのは何事も経験です。
+最初から完璧を求めるのは、傲慢だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ここは頑張るところです。イイ意味で、
+もっと、ずうずうしく考えるべきだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>君は運よく業界に滑り込めたんです。
+たくさん失敗できる環境に移れたんです</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>失敗からしか、経験と実力は得られない。
+そうしないと実力不足は補えません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そうなのかもしれません</t>
+  </si>
+  <si>
+    <t>でも……歌だけは、無理なんです</t>
+  </si>
+  <si>
+    <t>絞り出すように有希が言った。
+けれど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……その人の言った通りだよ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +298,70 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +551,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1060"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,670 +610,871 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" s="5" customFormat="1" ht="28.8" customHeight="1">
+      <c r="B8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" customHeight="1">
+      <c r="B9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.2" customHeight="1">
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I11" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" customHeight="1">
+      <c r="I12" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="27.6" customHeight="1">
+      <c r="I13" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="C14" s="9"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="B15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:12" ht="28.8" customHeight="1">
+      <c r="A16" s="1"/>
+      <c r="B16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="30" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="I20" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B24" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="B27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="B28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1">
+      <c r="B31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30" customHeight="1">
+      <c r="B32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" customHeight="1">
+      <c r="I36" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
       <c r="I37" s="1"/>
     </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
       <c r="I38" s="1"/>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
       <c r="I41" s="1"/>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
       <c r="I42" s="1"/>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" spans="1:10" ht="13.5" customHeight="1">
       <c r="I43" s="1"/>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+    <row r="44" spans="1:10" ht="13.5" customHeight="1">
       <c r="I44" s="1"/>
     </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
       <c r="I45" s="1"/>
     </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
       <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
       <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="1"/>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A57" s="1"/>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
       <c r="I58" s="1"/>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="I59" s="1"/>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1">
       <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
+      <c r="C65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
+    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
+      <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1">
       <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1">
       <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="C69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
+    <row r="70" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" ht="13.5" customHeight="1">
+    <row r="71" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
+      <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" spans="1:10" ht="13.5" customHeight="1">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" spans="1:10" ht="13.5" customHeight="1">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" ht="13.5" customHeight="1">
+    <row r="74" spans="1:10" ht="13.5" customHeight="1">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" spans="1:10" ht="13.5" customHeight="1">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
+    <row r="76" spans="1:10" ht="13.5" customHeight="1">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
+    <row r="77" spans="1:10" ht="13.5" customHeight="1">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
+    <row r="78" spans="1:10" ht="13.5" customHeight="1">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+    </row>
+    <row r="79" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
       <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
       <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
+      <c r="B84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A85" s="1"/>
       <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
       <c r="I85" s="1"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
       <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
+      <c r="C89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" ht="13.5" customHeight="1">
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="I100" s="1"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="1"/>
       <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="1"/>
+      <c r="H102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
       <c r="I108" s="1"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" ht="13.5" customHeight="1">
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A116" s="1"/>
       <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
       <c r="I116" s="1"/>
-    </row>
-    <row r="117" ht="13.5" customHeight="1">
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="1"/>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A124" s="1"/>
       <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
       <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" ht="13.5" customHeight="1">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
     </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-    </row>
-    <row r="132" ht="13.5" customHeight="1">
+    </row>
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" ht="13.5" customHeight="1">
+    </row>
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="H133" s="1"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+      <c r="H134" s="1"/>
       <c r="I134" s="1"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
       <c r="I137" s="1"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="138" spans="1:9" ht="13.5" customHeight="1">
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="143" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
     <row r="147" ht="13.5" customHeight="1"/>
@@ -1973,10 +2389,11 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0105.xlsx
+++ b/Assets/test260903/chapter0105.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB8A32F-0AA3-462D-8C8E-4938C6199CDF}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F7350B-4309-4E0A-9914-4D5F937B7AB9}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="199">
   <si>
     <t>Command</t>
   </si>
@@ -250,13 +250,661 @@
   </si>
   <si>
     <t>……その人の言った通りだよ</t>
+  </si>
+  <si>
+    <t>諦めちゃいけません。
+確かに貴方の歌唱力には問題がある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>けれど、だからこそ努力するんです。
+弱点から逃げちゃいけません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……マネージャーは静かに言った</t>
+  </si>
+  <si>
+    <t>一理あると思う。たしかに有希は幸運だ。
+一生に一度のチャンスを得たのだから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、僕は嫌いだ。こういうやり方は。
+だって今、有希は……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>はっ……はい……うぅ……</t>
+  </si>
+  <si>
+    <t>……泣いている。
+ずっと我慢していたのに、今は……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……どんな理屈だろうと、泣かすなよ。
+僕の一番好きな人を……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>分かったら、そこの君はどきなさい。
+それで、浪川さんは一緒に帰りましょう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マネージャー</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どきません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>えっ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……君くらいの年齢だと、
+今の話は理解できないでしょう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、理解できなくてもいいから、
+どいてください。これは仕事なんです</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「仕事」……その言葉に、
+あの日の編集さんの言葉が蘇った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「編集の仕事は、作家の才能を
+最高の形で世に出す手助けをすること」</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マネージャーの仕事だって同じはずだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>面倒を見る人物の才能と魅力を、
+最大限に高める仕事のはずだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>*選択肢0105-2-a</t>
+  </si>
+  <si>
+    <t>*選択肢0105-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>仕事だからでしょう</t>
+  </si>
+  <si>
+    <t>ん？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……！</t>
+  </si>
+  <si>
+    <t>この男はマネージャーなのに、
+有希のことを何も分かっていない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の一番の才能は、頑張れることだ。
+頑張りすぎるくらい頑張ることだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今、この男は……
+有希の一番の才能を潰そうとしている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>仕事だから、泣かせちゃダメだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>センセー……あなた……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>君は……やっぱり分かっていませんね</t>
+  </si>
+  <si>
+    <t>*選択肢0105-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希に重圧を背負わせすぎだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>重圧と向き合うのが、役者の仕事です</t>
+  </si>
+  <si>
+    <t>……違う。今の有希が背負っているのは、
+不本意な重圧だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それにマネージャーなら、
+無駄な重圧から彼女を守るべきだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あなたは子どもを泣かすのが仕事ですか？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>泣かずに成功した人間はいません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>苦労せずに、楽しく成功しようなんて、
+それこそ傲慢です</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>泣かさないように工夫しないのも傲慢です</t>
+  </si>
+  <si>
+    <t>……なるほど。君は君なりに、
+それなりの仕事観があるのですね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-7-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……有希を休ませてほしい。今すぐ</t>
+  </si>
+  <si>
+    <t>センセー……</t>
+  </si>
+  <si>
+    <t>ふぅ……いい機会だ。浪川さん。
+今ここで、どうするか決めてほしい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>君のために頑張ってくれた事務所のみんな、
+共演してくれた人、応援してくれてる人</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>みんなの期待に応えるために、
+これからも努力を続けて、責任を果たすか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>…………はい</t>
+  </si>
+  <si>
+    <t>それとも……彼の言う通りにするか。
+楽にはなるけど、成功はないよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>逃げだし、甘えだからね。
+そういう人間は絶対に成功しない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ここでハッキリと、君に決めてもらいたい</t>
+  </si>
+  <si>
+    <t>そうじゃないと、君とは仕事ができない。
+逃げ出す気の人は応援できないからね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……だと、思います</t>
+  </si>
+  <si>
+    <t>有希は別人のように弱々しく答えた</t>
+  </si>
+  <si>
+    <t>5分、5分です。
+今から5分だけ考える時間をあげます</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それで、結論を出してください</t>
+  </si>
+  <si>
+    <t>……はい、わかりました</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>沈黙が訪れた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ずっと考えている</t>
+  </si>
+  <si>
+    <t>今、言いたいことは一つしかない</t>
+  </si>
+  <si>
+    <t>有希に不幸になってほしくない。
+これ以上、有希に苦しんで欲しくない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから……</t>
+  </si>
+  <si>
+    <t>*選択肢0105-8-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希、ひとつだけ</t>
+  </si>
+  <si>
+    <t>……え？</t>
+  </si>
+  <si>
+    <t>*選択肢0105-9-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>どっちを選んでもいいと思う</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ほう？</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-10-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でも、絶対させないよ。こっちを選んだら</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>させないって……何を？</t>
+  </si>
+  <si>
+    <t>*選択肢0105-11-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>後悔なんてさ</t>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして、また沈黙が訪れた</t>
+  </si>
+  <si>
+    <t>重い時間がゆっくりと流れ、そして……</t>
+  </si>
+  <si>
+    <t>時間です。答えてください、浪川さん</t>
+  </si>
+  <si>
+    <t>有希……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>センセー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>私はね</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ずっと夢だったし、
+これから先も、絶対に諦めたくない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも……</t>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから……私、辞めます</t>
+  </si>
+  <si>
+    <t>BGM3</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>もう無理なんです。ごめんなさい</t>
+  </si>
+  <si>
+    <t>これは私のやりたいことじゃない。
+私の頑張りたいことじゃありません"</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これは一生に一回もない、
+奇跡みたいなチャンス……"</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>とっさに、僕は……</t>
+  </si>
+  <si>
+    <t>*選択肢0105-12-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希のマネージャーは、僕だ</t>
+  </si>
+  <si>
+    <t>終わった……やっと……</t>
+  </si>
+  <si>
+    <t>そう呟くと、有希が足元から崩れ落ちた。
+慌てて彼女を抱きとめる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>本当、何で頑張れないんやろうね……</t>
+  </si>
+  <si>
+    <t>*選択肢0105-13-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-13-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>頑張り方だって、人それぞれだ</t>
+  </si>
+  <si>
+    <t>有希は十分に頑張ったよ</t>
+  </si>
+  <si>
+    <t>……ありがとね、センセー……
+私も……そうだと思う……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-13合流</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>約束、守れんかったね……</t>
+  </si>
+  <si>
+    <t>Jump</t>
+  </si>
+  <si>
+    <t>ごめんね、私は……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ううん、まだ頑張れたって思う。
+私が実力不足やけん、こんなことに……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも……できたんじゃないかって思う。
+もっと頑張れたんじゃないかって</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……違う。有希は十分に頑張った。
+でも、頑張り方を間違えただけだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>せっかくのチャンスを活かせなくて、
+おまけに泣き出して……みっともない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ごめん……足から、力が抜けて……
+情けないっちゃね、私って……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>捨て台詞を残して男は去っていった。
+その途端に……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>は、なんだそりゃ。
+これだからガキの担当は嫌なんだよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これで終わりです。
+後悔しても、俺は知らないから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>吐き捨てるような最後の一言に、
+あの男の本性が見えた気がした</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>手続きとかは、今すぐ僕がやります。
+ただし……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そっか。
+君がそう言うなら、仕方ありません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希が深く頭を下げた。
+すると……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私は……ずっと頑張ってきたの。
+役者になって成功するために</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>椅子に深く座った有希は、
+目をつぶって、祈るような姿勢で……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-14-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-14-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>休もう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>いいんだよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0105-14合流</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……私、休むよ。
+凄く……疲れたけんさ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ホテルの部屋、ちょっと借りるね。
+床でもいいけん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ただ……眠ってしまう前に、
+これだけは言わせて</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>センセー……さっきさ、
+後悔させないって言ってくれたよね？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それでね……私、思ったんちゃ。
+絶対、絶対、しないに決まってる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大好きな人と一緒なんやもん。
+何がどうなっても、後悔せんっちゃ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……私ね、あなたが好き、大好き</t>
+  </si>
+  <si>
+    <t>ずっとね……ずっと前から、
+あなたが好きやとは思ってたけど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今がね……
+あなたのこと、一番好きっちゃ……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>眠った有希を背負って部屋に戻り、
+有希をベッドに寝かせ、僕は床に転がった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>翌朝、一睡もできなかった僕に、
+有希は「ありがとう」とだけ言った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして、部屋から出て行った</t>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +940,19 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -313,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -338,6 +999,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,14 +1227,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1060"/>
+  <dimension ref="A1:L1065"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="7" width="5.109375" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="9" max="9" width="39.5546875" customWidth="1"/>
     <col min="10" max="10" width="8.21875" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
@@ -1003,526 +1672,1387 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I38" s="1"/>
+    <row r="37" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1">
+      <c r="B38" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I39" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.2" customHeight="1">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
+      <c r="I40" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I41" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I45" s="1"/>
+      <c r="B42" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I43" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1">
+      <c r="I44" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30" customHeight="1">
+      <c r="B45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A47" s="1"/>
+      <c r="A47" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="B47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="B48" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="I50" s="1"/>
+    <row r="49" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B49" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" customHeight="1">
+      <c r="B50" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+    <row r="51" spans="1:10" ht="28.8" customHeight="1">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="I51" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="30.6" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="I52" s="1"/>
+      <c r="I52" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="I53" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+    <row r="54" spans="1:10" ht="28.8" customHeight="1">
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="I54" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="I55" s="7" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="I56" s="1"/>
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A57" s="1"/>
+      <c r="A57" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I58" s="1"/>
+      <c r="B58" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B59" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I60" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.8" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I61" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="31.2" customHeight="1">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
+      <c r="I62" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
+      <c r="A63" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="I63" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A64" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B65" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="13.2" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="B66" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+      <c r="A67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+      <c r="I67" s="7" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B69" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="30" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I70" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="27.6" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+      <c r="I71" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
+      <c r="A72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
+      <c r="I72" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A73" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="B74" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B75" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
+      <c r="A76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="I76" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
+    <row r="78" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B78" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B79" s="1"/>
+      <c r="A79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="C79" s="1"/>
-      <c r="I79" s="1"/>
+      <c r="I79" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B81" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B82" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B83" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="30.6" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="B84" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>107</v>
+      </c>
       <c r="J84" s="1"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="I85" s="1"/>
+      <c r="B85" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+    <row r="86" spans="1:10" ht="28.8" customHeight="1">
       <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
+      <c r="B86" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="31.8" customHeight="1">
+      <c r="B87" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="I89" s="1"/>
+      <c r="B88" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B89" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="I90" s="1"/>
+      <c r="B90" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I91" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="30" customHeight="1">
       <c r="A92" s="1"/>
+      <c r="B92" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
+      <c r="B93" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
+      <c r="B94" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
-      <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I95" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="28.8" customHeight="1">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="I96" s="7" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
+      <c r="I97" s="12" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I99" s="1"/>
+      <c r="I98" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="27.6" customHeight="1">
+      <c r="I99" s="7" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I100" s="1"/>
+      <c r="I100" s="12" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-      <c r="I101" s="1"/>
+      <c r="A101" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="1"/>
+      <c r="A102" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
+      <c r="B103" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B104" s="1"/>
+      <c r="A104" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="C104" s="1"/>
-      <c r="I104" s="1"/>
+      <c r="I104" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I106" s="1"/>
+      <c r="B106" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I107" s="1"/>
+      <c r="A107" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="I108" s="1"/>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I109" s="1"/>
+      <c r="B109" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
+      <c r="A110" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="C110" s="1"/>
-      <c r="I110" s="1"/>
+      <c r="I110" s="12" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="I112" s="1"/>
+      <c r="B112" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
-      <c r="I113" s="1"/>
+      <c r="I113" s="12" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
-      <c r="I114" s="1"/>
+      <c r="I114" s="12" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="I115" s="1"/>
+      <c r="B115" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J115" s="1"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
-      <c r="I116" s="1"/>
+      <c r="I116" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="J116" s="1"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="I117" s="1"/>
+      <c r="B117" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>139</v>
+      </c>
       <c r="J117" s="1"/>
     </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+    <row r="118" spans="1:10" ht="30" customHeight="1">
+      <c r="B118" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="28.8" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B119" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I119" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="30" customHeight="1">
       <c r="A120" s="1"/>
+      <c r="B120" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I120" s="11" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
+      <c r="B121" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="I122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
+      <c r="A122" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B122" s="8"/>
+      <c r="C122" s="9"/>
+      <c r="I122" s="12"/>
+    </row>
+    <row r="123" spans="1:10" ht="30" customHeight="1">
+      <c r="B123" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="30" customHeight="1">
+      <c r="A124" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C124" s="9"/>
+      <c r="I124" s="7"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
+      <c r="B125" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="1"/>
+      <c r="B126" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="30" customHeight="1">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="I127" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B128" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B129" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="30" customHeight="1">
+      <c r="A130" s="1"/>
+      <c r="B130" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I130" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="30" customHeight="1">
+      <c r="A131" s="1"/>
+      <c r="I131" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I132" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I133" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A134" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H135" s="1"/>
+      <c r="I135" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="B136" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H136" s="1"/>
+      <c r="I136" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A137" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C137" s="9"/>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1"/>
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" spans="1:9" ht="30" customHeight="1">
+      <c r="I138" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="30" customHeight="1">
+      <c r="B139" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" spans="1:9" ht="30" customHeight="1">
+      <c r="A140" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B141" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="28.2" customHeight="1">
+      <c r="I142" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B143" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B144" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B145" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="30" customHeight="1">
+      <c r="I146" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A147" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I147" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A148" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A149" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B150" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I150" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B151" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I151" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A152" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B152" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A153" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B154" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I154" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B155" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I155" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A157" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B158" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I158" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A159" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I159" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A160" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I160" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A161" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A164" t="s">
+        <v>161</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A165" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A166" s="5"/>
+      <c r="B166" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I166" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B167" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I167" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="30" customHeight="1">
+      <c r="B168" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I168" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B169" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I169" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="30" customHeight="1">
+      <c r="B170" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I170" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="30" customHeight="1">
+      <c r="B171" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I171" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B172" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I172" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B173" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I173" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B174" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I174" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B175" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I175" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="30" customHeight="1">
+      <c r="B176" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I176" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B177" s="8"/>
+      <c r="C177" s="9"/>
+      <c r="I177" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I178" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I179" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B180" t="s">
+        <v>33</v>
+      </c>
+      <c r="C180" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I126" s="1"/>
-    </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="I127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-    </row>
-    <row r="129" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I130" s="1"/>
-    </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I140" s="1"/>
-    </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I141" s="1"/>
-    </row>
-    <row r="142" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
-    <row r="177" ht="13.5" customHeight="1"/>
-    <row r="178" ht="13.5" customHeight="1"/>
-    <row r="179" ht="13.5" customHeight="1"/>
-    <row r="180" ht="13.5" customHeight="1"/>
-    <row r="181" ht="13.5" customHeight="1"/>
-    <row r="182" ht="13.5" customHeight="1"/>
-    <row r="183" ht="13.5" customHeight="1"/>
-    <row r="184" ht="13.5" customHeight="1"/>
-    <row r="185" ht="13.5" customHeight="1"/>
-    <row r="186" ht="13.5" customHeight="1"/>
-    <row r="187" ht="13.5" customHeight="1"/>
-    <row r="188" ht="13.5" customHeight="1"/>
-    <row r="189" ht="13.5" customHeight="1"/>
-    <row r="190" ht="13.5" customHeight="1"/>
-    <row r="191" ht="13.5" customHeight="1"/>
-    <row r="192" ht="13.5" customHeight="1"/>
+    </row>
+    <row r="182" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="183" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="184" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="185" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="186" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="188" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="189" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="190" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="192" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="193" ht="13.5" customHeight="1"/>
     <row r="194" ht="13.5" customHeight="1"/>
     <row r="195" ht="13.5" customHeight="1"/>
@@ -2391,6 +3921,11 @@
     <row r="1058" ht="13.5" customHeight="1"/>
     <row r="1059" ht="13.5" customHeight="1"/>
     <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0105.xlsx
+++ b/Assets/test260903/chapter0105.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="586" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F7350B-4309-4E0A-9914-4D5F937B7AB9}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E52C88-20E7-4D22-A309-101E3655EC5F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2811,8 +2811,8 @@
       </c>
     </row>
     <row r="156" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A156" t="s">
-        <v>161</v>
+      <c r="A156" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>159</v>

--- a/Assets/test260903/chapter0105.xlsx
+++ b/Assets/test260903/chapter0105.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E52C88-20E7-4D22-A309-101E3655EC5F}"/>
+  <xr:revisionPtr revIDLastSave="597" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E036D2C2-162B-4017-9468-3D79D7A4F9F9}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="202">
   <si>
     <t>Command</t>
   </si>
@@ -665,16 +665,6 @@
     <t>もう無理なんです。ごめんなさい</t>
   </si>
   <si>
-    <t>これは私のやりたいことじゃない。
-私の頑張りたいことじゃありません"</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>これは一生に一回もない、
-奇跡みたいなチャンス……"</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>とっさに、僕は……</t>
   </si>
   <si>
@@ -898,6 +888,35 @@
   </si>
   <si>
     <t>&lt;Off&gt;</t>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>倒れる音</t>
+    <rPh sb="0" eb="1">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これは一生に一回もない、
+奇跡みたいなチャンス……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これは私のやりたいことじゃない。
+私の頑張りたいことじゃありません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希は微笑んで、気を失うように眠った。
+それは、再会してから初めて見た笑顔だった</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1227,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1065"/>
+  <dimension ref="A1:L1066"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1486,7 +1505,12 @@
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="I20" s="7" t="s">
         <v>39</v>
       </c>
@@ -2246,7 +2270,7 @@
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="I96" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
@@ -2447,7 +2471,7 @@
         <v>26</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="28.8" customHeight="1">
@@ -2471,7 +2495,7 @@
         <v>26</v>
       </c>
       <c r="I120" s="11" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
@@ -2501,7 +2525,7 @@
         <v>26</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="30" customHeight="1">
@@ -2541,7 +2565,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="I127" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J127" s="1"/>
     </row>
@@ -2553,7 +2577,7 @@
         <v>26</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="28.8" customHeight="1">
@@ -2564,7 +2588,7 @@
         <v>26</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="30" customHeight="1">
@@ -2576,18 +2600,18 @@
         <v>26</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="30" customHeight="1">
       <c r="A131" s="1"/>
       <c r="I131" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="I132" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="13.5" customHeight="1">
@@ -2595,15 +2619,15 @@
         <v>77</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I133" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="13.5" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="13.5" customHeight="1">
@@ -2629,15 +2653,15 @@
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="28.8" customHeight="1">
       <c r="A137" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C137" s="9"/>
       <c r="G137">
@@ -2648,7 +2672,7 @@
     </row>
     <row r="138" spans="1:9" ht="30" customHeight="1">
       <c r="I138" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="30" customHeight="1">
@@ -2656,47 +2680,45 @@
         <v>65</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I139" s="7"/>
     </row>
     <row r="140" spans="1:9" ht="30" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G140">
         <v>1</v>
       </c>
       <c r="I140" s="7"/>
     </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B141" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C141" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I141" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="28.2" customHeight="1">
-      <c r="I142" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B143" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C143" s="9" t="s">
-        <v>26</v>
-      </c>
+    <row r="141" spans="1:9" ht="26.4" customHeight="1">
+      <c r="A141" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B142" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="28.2" customHeight="1">
       <c r="I143" s="7" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="28.8" customHeight="1">
@@ -2707,34 +2729,34 @@
         <v>26</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="28.8" customHeight="1">
       <c r="B145" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C145" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I145" s="12" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="30" customHeight="1">
-      <c r="I146" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A147" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I147" t="s">
-        <v>156</v>
+      <c r="I145" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B146" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="30" customHeight="1">
+      <c r="I147" s="7" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="13.5" customHeight="1">
@@ -2742,107 +2764,107 @@
         <v>66</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>157</v>
+        <v>152</v>
+      </c>
+      <c r="I148" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="13.5" customHeight="1">
       <c r="A149" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B150" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C150" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I150" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B151" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I151" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B152" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I152" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A153" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A154" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B155" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I155" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B156" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I156" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B151" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I151" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A152" s="13" t="s">
+    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A157" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B152" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A153" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B154" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C154" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I154" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B155" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C155" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I155" t="s">
+      <c r="B157" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A158" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B159" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I159" s="13" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A156" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A157" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B158" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C158" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I158" s="13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A159" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="13.5" customHeight="1">
@@ -2850,56 +2872,56 @@
         <v>66</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I160" s="13" t="s">
         <v>177</v>
-      </c>
-      <c r="I160" s="13" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="13.5" customHeight="1">
       <c r="A161" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I161" s="13" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="13.5" customHeight="1">
       <c r="A162" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B162" s="10" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A163" s="1" t="s">
-        <v>177</v>
+      <c r="B163" s="10" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A164" t="s">
-        <v>161</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>181</v>
+      <c r="A164" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A165" s="10" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A166" s="5"/>
-      <c r="B166" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C166" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I166" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A165" t="s">
+        <v>159</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A166" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A167" s="5"/>
       <c r="B167" s="8" t="s">
         <v>49</v>
       </c>
@@ -2907,7 +2929,7 @@
         <v>26</v>
       </c>
       <c r="I167" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="30" customHeight="1">
@@ -2918,7 +2940,7 @@
         <v>26</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="28.2" customHeight="1">
@@ -2929,7 +2951,7 @@
         <v>26</v>
       </c>
       <c r="I169" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="30" customHeight="1">
@@ -2940,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="30" customHeight="1">
@@ -2951,7 +2973,7 @@
         <v>26</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="13.5" customHeight="1">
@@ -2973,7 +2995,7 @@
         <v>26</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="13.5" customHeight="1">
@@ -2984,7 +3006,7 @@
         <v>26</v>
       </c>
       <c r="I174" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="28.8" customHeight="1">
@@ -2995,7 +3017,7 @@
         <v>26</v>
       </c>
       <c r="I175" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="30" customHeight="1">
@@ -3006,43 +3028,49 @@
         <v>26</v>
       </c>
       <c r="I176" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" ht="28.2" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="30" customHeight="1">
       <c r="B177" s="8"/>
       <c r="C177" s="9"/>
       <c r="I177" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B178" s="8"/>
+      <c r="C178" s="9"/>
+      <c r="I178" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I179" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I180" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="30.6" customHeight="1">
-      <c r="I178" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I179" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B180" t="s">
+    <row r="181" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B181" t="s">
         <v>33</v>
       </c>
-      <c r="C180" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A181" s="1" t="s">
+      <c r="C181" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A182" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="183" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="184" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="185" spans="1:9" ht="13.5" customHeight="1"/>
@@ -3926,6 +3954,7 @@
     <row r="1063" ht="13.5" customHeight="1"/>
     <row r="1064" ht="13.5" customHeight="1"/>
     <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0105.xlsx
+++ b/Assets/test260903/chapter0105.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="597" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E036D2C2-162B-4017-9468-3D79D7A4F9F9}"/>
+  <xr:revisionPtr revIDLastSave="676" documentId="11_9CD6F5F8FBE188052E83A027A8BF20349734D0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33063102-C2A0-49D2-93B2-3B9D711822B9}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="207">
   <si>
     <t>Command</t>
   </si>
@@ -916,6 +916,22 @@
   <si>
     <t>有希は微笑んで、気を失うように眠った。
 それは、再会してから初めて見た笑顔だった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悲しみ</t>
+  </si>
+  <si>
+    <t>照れ</t>
+  </si>
+  <si>
+    <t>喜び</t>
+  </si>
+  <si>
+    <t>通常</t>
+  </si>
+  <si>
+    <t>喜び</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1444,8 +1460,8 @@
       <c r="B15" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>26</v>
+      <c r="C15" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="G15" s="1"/>
       <c r="I15" s="1" t="s">
@@ -1459,7 +1475,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>34</v>
@@ -1472,7 +1488,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>35</v>
@@ -1484,7 +1500,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>36</v>
@@ -1509,7 +1525,7 @@
         <v>33</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>39</v>
@@ -1521,7 +1537,7 @@
         <v>33</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>40</v>
@@ -1533,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="7" t="s">
@@ -1545,7 +1561,7 @@
         <v>33</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>42</v>
@@ -1556,7 +1572,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>43</v>
@@ -1568,7 +1584,7 @@
         <v>33</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>44</v>
@@ -1628,8 +1644,8 @@
       <c r="B30" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>26</v>
+      <c r="C30" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>38</v>
@@ -1662,8 +1678,8 @@
       <c r="B33" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>26</v>
+      <c r="C33" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>52</v>
@@ -1673,8 +1689,8 @@
       <c r="B34" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>26</v>
+      <c r="C34" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>53</v>
@@ -1684,8 +1700,8 @@
       <c r="B35" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>26</v>
+      <c r="C35" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>39</v>
@@ -1741,8 +1757,8 @@
       <c r="B42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>26</v>
+      <c r="C42" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>61</v>
@@ -1792,8 +1808,8 @@
       <c r="B48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>26</v>
+      <c r="C48" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>69</v>
@@ -1892,8 +1908,8 @@
       <c r="B59" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>26</v>
+      <c r="C59" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>82</v>
@@ -1944,8 +1960,8 @@
       <c r="B65" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>26</v>
+      <c r="C65" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>88</v>
@@ -2107,8 +2123,8 @@
       <c r="B81" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>26</v>
+      <c r="C81" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>104</v>
@@ -2154,8 +2170,8 @@
       <c r="B85" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>26</v>
+      <c r="C85" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>108</v>
@@ -2211,8 +2227,8 @@
       <c r="B90" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>26</v>
+      <c r="C90" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>113</v>
@@ -2252,8 +2268,8 @@
       <c r="B94" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C94" s="9" t="s">
-        <v>26</v>
+      <c r="C94" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>117</v>
@@ -2318,8 +2334,8 @@
       <c r="B103" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C103" s="9" t="s">
-        <v>26</v>
+      <c r="C103" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>125</v>
@@ -2377,8 +2393,8 @@
       <c r="B109" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C109" s="9" t="s">
-        <v>26</v>
+      <c r="C109" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I109" s="12" t="s">
         <v>131</v>
@@ -2408,8 +2424,8 @@
       <c r="B112" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C112" s="9" t="s">
-        <v>26</v>
+      <c r="C112" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I112" s="12" t="s">
         <v>134</v>
@@ -2455,8 +2471,8 @@
       <c r="B117" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C117" s="9" t="s">
-        <v>26</v>
+      <c r="C117" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>139</v>
@@ -2468,7 +2484,7 @@
         <v>49</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>173</v>
@@ -2480,7 +2496,7 @@
         <v>49</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I119" s="11" t="s">
         <v>140</v>
@@ -2492,7 +2508,7 @@
         <v>49</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>199</v>
@@ -2502,8 +2518,8 @@
       <c r="B121" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C121" s="9" t="s">
-        <v>26</v>
+      <c r="C121" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>141</v>
@@ -2554,8 +2570,8 @@
       <c r="B126" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C126" s="9" t="s">
-        <v>26</v>
+      <c r="C126" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>145</v>
@@ -2635,8 +2651,8 @@
       <c r="B135" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C135" s="9" t="s">
-        <v>26</v>
+      <c r="C135" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="12" t="s">
@@ -2709,8 +2725,8 @@
       <c r="B142" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C142" s="9" t="s">
-        <v>26</v>
+      <c r="C142" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>149</v>
@@ -2726,7 +2742,7 @@
         <v>49</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>165</v>
@@ -2737,7 +2753,7 @@
         <v>49</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>164</v>
@@ -2747,8 +2763,8 @@
       <c r="B146" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C146" s="9" t="s">
-        <v>26</v>
+      <c r="C146" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>151</v>
@@ -2791,7 +2807,7 @@
         <v>49</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="I151" s="14" t="s">
         <v>156</v>
@@ -2802,7 +2818,7 @@
         <v>49</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>162</v>
@@ -2826,7 +2842,7 @@
         <v>49</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I155" s="11" t="s">
         <v>161</v>
@@ -2836,8 +2852,8 @@
       <c r="B156" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C156" s="9" t="s">
-        <v>26</v>
+      <c r="C156" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I156" t="s">
         <v>158</v>
@@ -2860,8 +2876,8 @@
       <c r="B159" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C159" s="9" t="s">
-        <v>26</v>
+      <c r="C159" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>160</v>
@@ -2926,7 +2942,7 @@
         <v>49</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I167" s="11" t="s">
         <v>180</v>
@@ -2937,7 +2953,7 @@
         <v>49</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>181</v>
@@ -2970,7 +2986,7 @@
         <v>49</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="I171" s="11" t="s">
         <v>184</v>
@@ -2980,8 +2996,8 @@
       <c r="B172" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C172" s="9" t="s">
-        <v>26</v>
+      <c r="C172" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="I172" t="s">
         <v>133</v>
@@ -2992,7 +3008,7 @@
         <v>49</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="I173" s="11" t="s">
         <v>185</v>
@@ -3002,8 +3018,8 @@
       <c r="B174" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C174" s="9" t="s">
-        <v>26</v>
+      <c r="C174" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="I174" t="s">
         <v>186</v>
@@ -3014,7 +3030,7 @@
         <v>49</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="I175" s="11" t="s">
         <v>187</v>
@@ -3025,15 +3041,19 @@
         <v>49</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="30" customHeight="1">
-      <c r="B177" s="8"/>
-      <c r="C177" s="9"/>
+      <c r="B177" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>195</v>
+      </c>
       <c r="I177" s="11" t="s">
         <v>201</v>
       </c>
@@ -3056,12 +3076,8 @@
       </c>
     </row>
     <row r="181" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B181" t="s">
-        <v>33</v>
-      </c>
-      <c r="C181" s="13" t="s">
-        <v>195</v>
-      </c>
+      <c r="B181" s="13"/>
+      <c r="C181" s="13"/>
     </row>
     <row r="182" spans="1:9" ht="13.5" customHeight="1">
       <c r="A182" s="1" t="s">
